--- a/upload/plano-cuidado-multi.xlsx
+++ b/upload/plano-cuidado-multi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="17">
   <si>
     <t>unidade</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -874,13 +874,13 @@
         <v>4</v>
       </c>
       <c r="D24" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E24" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F24" s="4">
-        <v>0.52500000000000002</v>
+        <v>0.53658536585365857</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1074,13 +1074,13 @@
         <v>2</v>
       </c>
       <c r="D34" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E34" s="3">
         <v>42</v>
       </c>
       <c r="F34" s="4">
-        <v>0.42857142857142855</v>
+        <v>0.45238095238095238</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1105,22 +1105,22 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" s="2">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C36" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F36" s="4">
-        <v>3.0303030303030304E-2</v>
+        <v>0.61904761904761907</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1128,19 +1128,19 @@
         <v>7</v>
       </c>
       <c r="B37" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C37" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
       </c>
       <c r="E37" s="3">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F37" s="4">
-        <v>2.2222222222222223E-2</v>
+        <v>3.0303030303030304E-2</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1151,16 +1151,16 @@
         <v>2023</v>
       </c>
       <c r="C38" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
       </c>
       <c r="E38" s="3">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F38" s="4">
-        <v>3.4482758620689655E-2</v>
+        <v>2.2222222222222223E-2</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1171,16 +1171,16 @@
         <v>2023</v>
       </c>
       <c r="C39" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3">
         <v>29</v>
       </c>
       <c r="F39" s="4">
-        <v>6.8965517241379309E-2</v>
+        <v>3.4482758620689655E-2</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1191,16 +1191,16 @@
         <v>2023</v>
       </c>
       <c r="C40" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D40" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40" s="3">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F40" s="4">
-        <v>8.8888888888888892E-2</v>
+        <v>6.8965517241379309E-2</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1208,19 +1208,19 @@
         <v>7</v>
       </c>
       <c r="B41" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D41" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" s="4">
-        <v>4.3478260869565216E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1231,16 +1231,16 @@
         <v>2024</v>
       </c>
       <c r="C42" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F42" s="4">
-        <v>0.02</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1251,16 +1251,16 @@
         <v>2024</v>
       </c>
       <c r="C43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E43" s="3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F43" s="4">
-        <v>0.13461538461538461</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1271,16 +1271,16 @@
         <v>2024</v>
       </c>
       <c r="C44" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E44" s="3">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F44" s="4">
-        <v>0.28947368421052633</v>
+        <v>0.13461538461538461</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1291,16 +1291,16 @@
         <v>2024</v>
       </c>
       <c r="C45" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E45" s="3">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F45" s="4">
-        <v>0.30303030303030304</v>
+        <v>0.28947368421052633</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1311,36 +1311,36 @@
         <v>2024</v>
       </c>
       <c r="C46" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D46" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E46" s="3">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F46" s="4">
-        <v>0.47499999999999998</v>
+        <v>0.30303030303030304</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B47" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C47" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E47" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F47" s="4">
-        <v>1</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1348,39 +1348,39 @@
         <v>8</v>
       </c>
       <c r="B48" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C48" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
       </c>
       <c r="E48" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F48" s="4">
-        <v>5.2631578947368418E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="2">
         <v>2024</v>
       </c>
       <c r="C49" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
       <c r="E49" s="3">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F49" s="4">
-        <v>1.4705882352941176E-2</v>
+        <v>5.2631578947368418E-2</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1391,16 +1391,16 @@
         <v>2024</v>
       </c>
       <c r="C50" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
       </c>
       <c r="E50" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F50" s="4">
-        <v>1.3157894736842105E-2</v>
+        <v>1.4705882352941176E-2</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1411,16 +1411,16 @@
         <v>2024</v>
       </c>
       <c r="C51" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
       </c>
       <c r="E51" s="3">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F51" s="4">
-        <v>1.2345679012345678E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1431,16 +1431,16 @@
         <v>2024</v>
       </c>
       <c r="C52" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
       </c>
       <c r="E52" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F52" s="4">
-        <v>1.1627906976744186E-2</v>
+        <v>1.2345679012345678E-2</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1448,19 +1448,19 @@
         <v>9</v>
       </c>
       <c r="B53" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D53" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E53" s="3">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F53" s="4">
-        <v>5.7142857142857141E-2</v>
+        <v>1.1627906976744186E-2</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1471,16 +1471,16 @@
         <v>2025</v>
       </c>
       <c r="C54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F54" s="4">
-        <v>1.4705882352941176E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1491,16 +1491,16 @@
         <v>2025</v>
       </c>
       <c r="C55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E55" s="3">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F55" s="4">
-        <v>0.12820512820512819</v>
+        <v>1.4705882352941176E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1511,16 +1511,16 @@
         <v>2025</v>
       </c>
       <c r="C56" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E56" s="3">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F56" s="4">
-        <v>0.2</v>
+        <v>0.12820512820512819</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1531,16 +1531,16 @@
         <v>2025</v>
       </c>
       <c r="C57" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" s="3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E57" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F57" s="4">
-        <v>0.35294117647058826</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1551,16 +1551,16 @@
         <v>2025</v>
       </c>
       <c r="C58" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E58" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F58" s="4">
-        <v>0.42424242424242425</v>
+        <v>0.35294117647058826</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1571,16 +1571,16 @@
         <v>2025</v>
       </c>
       <c r="C59" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E59" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F59" s="4">
-        <v>0.26153846153846155</v>
+        <v>0.42424242424242425</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1591,16 +1591,16 @@
         <v>2025</v>
       </c>
       <c r="C60" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E60" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F60" s="4">
-        <v>0.29850746268656714</v>
+        <v>0.26153846153846155</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1611,16 +1611,16 @@
         <v>2025</v>
       </c>
       <c r="C61" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D61" s="3">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E61" s="3">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F61" s="4">
-        <v>0.39189189189189189</v>
+        <v>0.29850746268656714</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1631,16 +1631,16 @@
         <v>2025</v>
       </c>
       <c r="C62" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D62" s="3">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E62" s="3">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F62" s="4">
-        <v>0.28358208955223879</v>
+        <v>0.39189189189189189</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -1651,16 +1651,16 @@
         <v>2025</v>
       </c>
       <c r="C63" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D63" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E63" s="3">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F63" s="4">
-        <v>0.34920634920634919</v>
+        <v>0.28358208955223879</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -1671,16 +1671,16 @@
         <v>2025</v>
       </c>
       <c r="C64" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D64" s="3">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E64" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F64" s="4">
-        <v>0.22580645161290322</v>
+        <v>0.34920634920634919</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -1688,19 +1688,19 @@
         <v>9</v>
       </c>
       <c r="B65" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C65" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D65" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E65" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F65" s="4">
-        <v>0.23809523809523808</v>
+        <v>0.22580645161290322</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -1711,16 +1711,16 @@
         <v>2026</v>
       </c>
       <c r="C66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E66" s="3">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F66" s="4">
-        <v>0.23684210526315788</v>
+        <v>0.23809523809523808</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -1731,481 +1731,481 @@
         <v>2026</v>
       </c>
       <c r="C67" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E67" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F67" s="4">
-        <v>0.2</v>
+        <v>0.23684210526315788</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B68" s="2">
         <v>2026</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E68" s="3">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="F68" s="4">
-        <v>5.2631578947368418E-2</v>
+        <v>0.21333333333333335</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B69" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C69" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D69" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E69" s="3">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="F69" s="4">
-        <v>1.5544041450777202E-2</v>
+        <v>0.35135135135135137</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C70" s="2">
+        <v>5</v>
+      </c>
+      <c r="D70" s="3">
+        <v>1</v>
+      </c>
+      <c r="E70" s="3">
         <v>11</v>
       </c>
-      <c r="B70" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C70" s="2">
-        <v>2</v>
-      </c>
-      <c r="D70" s="3">
-        <v>1</v>
-      </c>
-      <c r="E70" s="3">
-        <v>152</v>
-      </c>
       <c r="F70" s="4">
-        <v>6.5789473684210523E-3</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B71" s="2">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="C71" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
       </c>
       <c r="E71" s="3">
-        <v>788</v>
+        <v>3</v>
       </c>
       <c r="F71" s="4">
-        <v>1.2690355329949238E-3</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B72" s="2">
         <v>2024</v>
       </c>
       <c r="C72" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
       </c>
       <c r="E72" s="3">
-        <v>328</v>
+        <v>3</v>
       </c>
       <c r="F72" s="4">
-        <v>3.0487804878048782E-3</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B73" s="2">
         <v>2024</v>
       </c>
       <c r="C73" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D73" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E73" s="3">
-        <v>375</v>
+        <v>57</v>
       </c>
       <c r="F73" s="4">
-        <v>3.2000000000000001E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B74" s="2">
         <v>2024</v>
       </c>
       <c r="C74" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D74" s="3">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3">
-        <v>352</v>
+        <v>2</v>
       </c>
       <c r="F74" s="4">
-        <v>0.21022727272727273</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B75" s="2">
         <v>2024</v>
       </c>
       <c r="C75" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D75" s="3">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="E75" s="3">
-        <v>214</v>
+        <v>9</v>
       </c>
       <c r="F75" s="4">
-        <v>0.5</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B76" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C76" s="2">
+        <v>2</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1</v>
+      </c>
+      <c r="E76" s="3">
         <v>11</v>
       </c>
-      <c r="D76" s="3">
-        <v>91</v>
-      </c>
-      <c r="E76" s="3">
-        <v>230</v>
-      </c>
       <c r="F76" s="4">
-        <v>0.39565217391304347</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B77" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C77" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D77" s="3">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="E77" s="3">
-        <v>274</v>
+        <v>8</v>
       </c>
       <c r="F77" s="4">
-        <v>0.37956204379562042</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B78" s="2">
         <v>2025</v>
       </c>
       <c r="C78" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D78" s="3">
-        <v>165</v>
+        <v>2</v>
       </c>
       <c r="E78" s="3">
-        <v>285</v>
+        <v>7</v>
       </c>
       <c r="F78" s="4">
-        <v>0.57894736842105265</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B79" s="2">
         <v>2025</v>
       </c>
       <c r="C79" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D79" s="3">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="E79" s="3">
-        <v>243</v>
+        <v>5</v>
       </c>
       <c r="F79" s="4">
-        <v>0.85185185185185186</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B80" s="2">
         <v>2025</v>
       </c>
       <c r="C80" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D80" s="3">
-        <v>237</v>
+        <v>1</v>
       </c>
       <c r="E80" s="3">
-        <v>280</v>
+        <v>7</v>
       </c>
       <c r="F80" s="4">
-        <v>0.84642857142857142</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B81" s="2">
         <v>2025</v>
       </c>
       <c r="C81" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D81" s="3">
-        <v>221</v>
+        <v>1</v>
       </c>
       <c r="E81" s="3">
-        <v>272</v>
+        <v>8</v>
       </c>
       <c r="F81" s="4">
-        <v>0.8125</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C82" s="2">
+        <v>9</v>
+      </c>
+      <c r="D82" s="3">
+        <v>1</v>
+      </c>
+      <c r="E82" s="3">
         <v>13</v>
       </c>
-      <c r="B82" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C82" s="2">
-        <v>5</v>
-      </c>
-      <c r="D82" s="3">
-        <v>211</v>
-      </c>
-      <c r="E82" s="3">
-        <v>287</v>
-      </c>
       <c r="F82" s="4">
-        <v>0.73519163763066198</v>
+        <v>7.6923076923076927E-2</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B83" s="2">
         <v>2025</v>
       </c>
       <c r="C83" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D83" s="3">
-        <v>216</v>
+        <v>1</v>
       </c>
       <c r="E83" s="3">
-        <v>273</v>
+        <v>10</v>
       </c>
       <c r="F83" s="4">
-        <v>0.79120879120879117</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B84" s="2">
         <v>2025</v>
       </c>
       <c r="C84" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D84" s="3">
-        <v>215</v>
+        <v>1</v>
       </c>
       <c r="E84" s="3">
-        <v>292</v>
+        <v>14</v>
       </c>
       <c r="F84" s="4">
-        <v>0.73630136986301364</v>
+        <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B85" s="2">
         <v>2025</v>
       </c>
       <c r="C85" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D85" s="3">
-        <v>212</v>
+        <v>3</v>
       </c>
       <c r="E85" s="3">
-        <v>268</v>
+        <v>16</v>
       </c>
       <c r="F85" s="4">
-        <v>0.79104477611940294</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B86" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C86" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D86" s="3">
-        <v>183</v>
+        <v>3</v>
       </c>
       <c r="E86" s="3">
-        <v>239</v>
+        <v>19</v>
       </c>
       <c r="F86" s="4">
-        <v>0.76569037656903771</v>
+        <v>0.15789473684210525</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B87" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C87" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D87" s="3">
-        <v>164</v>
+        <v>3</v>
       </c>
       <c r="E87" s="3">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="F87" s="4">
-        <v>0.66938775510204085</v>
+        <v>6.9767441860465115E-2</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B88" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C88" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D88" s="3">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="E88" s="3">
-        <v>254</v>
+        <v>58</v>
       </c>
       <c r="F88" s="4">
-        <v>0.60629921259842523</v>
+        <v>0.10344827586206896</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B89" s="2">
         <v>2025</v>
       </c>
       <c r="C89" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D89" s="3">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="E89" s="3">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="F89" s="4">
-        <v>0.56106870229007633</v>
+        <v>1.5544041450777202E-2</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
       </c>
       <c r="C90" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="E90" s="3">
-        <v>273</v>
+        <v>152</v>
       </c>
       <c r="F90" s="4">
-        <v>0.46886446886446886</v>
+        <v>6.5789473684210523E-3</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
@@ -2214,13 +2214,13 @@
         <v>2</v>
       </c>
       <c r="D91" s="3">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="E91" s="3">
-        <v>322</v>
+        <v>788</v>
       </c>
       <c r="F91" s="4">
-        <v>0.37267080745341613</v>
+        <v>1.2690355329949238E-3</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2228,459 +2228,459 @@
         <v>13</v>
       </c>
       <c r="B92" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C92" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D92" s="3">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="E92" s="3">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F92" s="4">
-        <v>0.57098765432098764</v>
+        <v>3.0487804878048782E-3</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B93" s="2">
         <v>2024</v>
       </c>
       <c r="C93" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D93" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E93" s="3">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="F93" s="4">
-        <v>2.4813895781637717E-3</v>
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B94" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C94" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D94" s="3">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E94" s="3">
-        <v>87</v>
+        <v>352</v>
       </c>
       <c r="F94" s="4">
-        <v>1.1494252873563218E-2</v>
+        <v>0.21022727272727273</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B95" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C95" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D95" s="3">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="E95" s="3">
-        <v>96</v>
+        <v>214</v>
       </c>
       <c r="F95" s="4">
-        <v>4.1666666666666664E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B96" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C96" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D96" s="3">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="E96" s="3">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="F96" s="4">
-        <v>0.05</v>
+        <v>0.39565217391304347</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B97" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C97" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D97" s="3">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="E97" s="3">
-        <v>40</v>
+        <v>274</v>
       </c>
       <c r="F97" s="4">
-        <v>0.25</v>
+        <v>0.37956204379562042</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B98" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C98" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D98" s="3">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="E98" s="3">
-        <v>90</v>
+        <v>285</v>
       </c>
       <c r="F98" s="4">
-        <v>0.87777777777777777</v>
+        <v>0.57894736842105265</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B99" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C99" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D99" s="3">
-        <v>67</v>
+        <v>207</v>
       </c>
       <c r="E99" s="3">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="F99" s="4">
-        <v>0.88157894736842102</v>
+        <v>0.85185185185185186</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B100" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C100" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D100" s="3">
-        <v>104</v>
+        <v>237</v>
       </c>
       <c r="E100" s="3">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="F100" s="4">
-        <v>0.92035398230088494</v>
+        <v>0.84642857142857142</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B101" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C101" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D101" s="3">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="E101" s="3">
-        <v>88</v>
+        <v>272</v>
       </c>
       <c r="F101" s="4">
-        <v>0.84090909090909094</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B102" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C102" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D102" s="3">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="E102" s="3">
-        <v>80</v>
+        <v>287</v>
       </c>
       <c r="F102" s="4">
-        <v>1</v>
+        <v>0.73519163763066198</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B103" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C103" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D103" s="3">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="E103" s="3">
-        <v>96</v>
+        <v>273</v>
       </c>
       <c r="F103" s="4">
-        <v>0.9375</v>
+        <v>0.79120879120879117</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B104" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C104" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D104" s="3">
-        <v>72</v>
+        <v>215</v>
       </c>
       <c r="E104" s="3">
-        <v>75</v>
+        <v>292</v>
       </c>
       <c r="F104" s="4">
-        <v>0.96</v>
+        <v>0.73630136986301364</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B105" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C105" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D105" s="3">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="E105" s="3">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="F105" s="4">
-        <v>1.1025641025641026</v>
+        <v>0.79104477611940294</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B106" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C106" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D106" s="3">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="E106" s="3">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="F106" s="4">
-        <v>0.92682926829268297</v>
+        <v>0.76569037656903771</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B107" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C107" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D107" s="3">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E107" s="3">
-        <v>69</v>
+        <v>245</v>
       </c>
       <c r="F107" s="4">
-        <v>1.1884057971014492</v>
+        <v>0.66938775510204085</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B108" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C108" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D108" s="3">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="E108" s="3">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="F108" s="4">
-        <v>1.0975609756097562</v>
+        <v>0.60629921259842523</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B109" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C109" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D109" s="3">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="E109" s="3">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="F109" s="4">
-        <v>1.0506329113924051</v>
+        <v>0.56106870229007633</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B110" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C110" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D110" s="3">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="E110" s="3">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="F110" s="4">
-        <v>1.1466666666666667</v>
+        <v>0.46886446886446886</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B111" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C111" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D111" s="3">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E111" s="3">
-        <v>57</v>
+        <v>322</v>
       </c>
       <c r="F111" s="4">
-        <v>1.0526315789473684</v>
+        <v>0.37267080745341613</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B112" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C112" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D112" s="3">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="E112" s="3">
-        <v>85</v>
+        <v>325</v>
       </c>
       <c r="F112" s="4">
-        <v>1.1176470588235294</v>
+        <v>0.58769230769230774</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B113" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C113" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D113" s="3">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="E113" s="3">
-        <v>62</v>
+        <v>293</v>
       </c>
       <c r="F113" s="4">
-        <v>1.3225806451612903</v>
+        <v>0.56655290102389078</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B114" s="2">
         <v>2024</v>
       </c>
       <c r="C114" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D114" s="3">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="E114" s="3">
-        <v>55</v>
+        <v>403</v>
       </c>
       <c r="F114" s="4">
-        <v>1.4727272727272727</v>
+        <v>2.4813895781637717E-3</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -2688,19 +2688,19 @@
         <v>15</v>
       </c>
       <c r="B115" s="2">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C115" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D115" s="3">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="E115" s="3">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F115" s="4">
-        <v>1.2948717948717949</v>
+        <v>1.1494252873563218E-2</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -2708,19 +2708,19 @@
         <v>15</v>
       </c>
       <c r="B116" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C116" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D116" s="3">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="E116" s="3">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="F116" s="4">
-        <v>1.2181818181818183</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -2728,19 +2728,19 @@
         <v>15</v>
       </c>
       <c r="B117" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C117" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D117" s="3">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="E117" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F117" s="4">
-        <v>1.2051282051282051</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -2748,19 +2748,19 @@
         <v>15</v>
       </c>
       <c r="B118" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C118" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D118" s="3">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="E118" s="3">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="F118" s="4">
-        <v>1.1481481481481481</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -2768,19 +2768,19 @@
         <v>15</v>
       </c>
       <c r="B119" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C119" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D119" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E119" s="3">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F119" s="4">
-        <v>1.0547945205479452</v>
+        <v>0.87777777777777777</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -2788,19 +2788,19 @@
         <v>15</v>
       </c>
       <c r="B120" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C120" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D120" s="3">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E120" s="3">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F120" s="4">
-        <v>1.1097560975609757</v>
+        <v>0.88157894736842102</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -2808,19 +2808,19 @@
         <v>15</v>
       </c>
       <c r="B121" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C121" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D121" s="3">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E121" s="3">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="F121" s="4">
-        <v>1.1643835616438356</v>
+        <v>0.92035398230088494</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -2828,19 +2828,19 @@
         <v>15</v>
       </c>
       <c r="B122" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C122" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D122" s="3">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E122" s="3">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F122" s="4">
-        <v>1.1408450704225352</v>
+        <v>0.84090909090909094</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -2848,19 +2848,19 @@
         <v>15</v>
       </c>
       <c r="B123" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C123" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D123" s="3">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E123" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F123" s="4">
-        <v>1.1621621621621621</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -2868,19 +2868,19 @@
         <v>15</v>
       </c>
       <c r="B124" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C124" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E124" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F124" s="4">
-        <v>1.1263157894736842</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -2888,19 +2888,19 @@
         <v>15</v>
       </c>
       <c r="B125" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C125" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D125" s="3">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E125" s="3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F125" s="4">
-        <v>1.2153846153846153</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -2908,19 +2908,19 @@
         <v>15</v>
       </c>
       <c r="B126" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C126" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D126" s="3">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E126" s="3">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F126" s="4">
-        <v>1.1911764705882353</v>
+        <v>1.1025641025641026</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -2928,19 +2928,19 @@
         <v>15</v>
       </c>
       <c r="B127" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C127" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D127" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E127" s="3">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F127" s="4">
-        <v>1.0714285714285714</v>
+        <v>0.92682926829268297</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -2948,19 +2948,19 @@
         <v>15</v>
       </c>
       <c r="B128" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C128" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D128" s="3">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E128" s="3">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F128" s="4">
-        <v>1.0845070422535212</v>
+        <v>1.1884057971014492</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -2968,79 +2968,539 @@
         <v>15</v>
       </c>
       <c r="B129" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C129" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D129" s="3">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E129" s="3">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F129" s="4">
-        <v>1.058139534883721</v>
+        <v>1.0975609756097562</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B130" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C130" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D130" s="3">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="E130" s="3">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F130" s="4">
-        <v>2.3255813953488372E-2</v>
+        <v>1.0506329113924051</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B131" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C131" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D131" s="3">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="E131" s="3">
-        <v>557</v>
+        <v>75</v>
       </c>
       <c r="F131" s="4">
-        <v>1.7953321364452424E-3</v>
+        <v>1.1466666666666667</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C132" s="2">
+        <v>9</v>
+      </c>
+      <c r="D132" s="3">
+        <v>60</v>
+      </c>
+      <c r="E132" s="3">
+        <v>57</v>
+      </c>
+      <c r="F132" s="4">
+        <v>1.0526315789473684</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C133" s="2">
+        <v>10</v>
+      </c>
+      <c r="D133" s="3">
+        <v>95</v>
+      </c>
+      <c r="E133" s="3">
+        <v>85</v>
+      </c>
+      <c r="F133" s="4">
+        <v>1.1176470588235294</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C134" s="2">
+        <v>11</v>
+      </c>
+      <c r="D134" s="3">
+        <v>82</v>
+      </c>
+      <c r="E134" s="3">
+        <v>62</v>
+      </c>
+      <c r="F134" s="4">
+        <v>1.3225806451612903</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C135" s="2">
+        <v>12</v>
+      </c>
+      <c r="D135" s="3">
+        <v>81</v>
+      </c>
+      <c r="E135" s="3">
+        <v>55</v>
+      </c>
+      <c r="F135" s="4">
+        <v>1.4727272727272727</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C136" s="2">
+        <v>1</v>
+      </c>
+      <c r="D136" s="3">
+        <v>101</v>
+      </c>
+      <c r="E136" s="3">
+        <v>78</v>
+      </c>
+      <c r="F136" s="4">
+        <v>1.2948717948717949</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C137" s="2">
+        <v>2</v>
+      </c>
+      <c r="D137" s="3">
+        <v>67</v>
+      </c>
+      <c r="E137" s="3">
+        <v>55</v>
+      </c>
+      <c r="F137" s="4">
+        <v>1.2181818181818183</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C138" s="2">
+        <v>3</v>
+      </c>
+      <c r="D138" s="3">
+        <v>94</v>
+      </c>
+      <c r="E138" s="3">
+        <v>78</v>
+      </c>
+      <c r="F138" s="4">
+        <v>1.2051282051282051</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C139" s="2">
+        <v>4</v>
+      </c>
+      <c r="D139" s="3">
+        <v>93</v>
+      </c>
+      <c r="E139" s="3">
+        <v>81</v>
+      </c>
+      <c r="F139" s="4">
+        <v>1.1481481481481481</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C140" s="2">
+        <v>5</v>
+      </c>
+      <c r="D140" s="3">
+        <v>77</v>
+      </c>
+      <c r="E140" s="3">
+        <v>73</v>
+      </c>
+      <c r="F140" s="4">
+        <v>1.0547945205479452</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C141" s="2">
+        <v>6</v>
+      </c>
+      <c r="D141" s="3">
+        <v>91</v>
+      </c>
+      <c r="E141" s="3">
+        <v>82</v>
+      </c>
+      <c r="F141" s="4">
+        <v>1.1097560975609757</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C142" s="2">
+        <v>7</v>
+      </c>
+      <c r="D142" s="3">
+        <v>85</v>
+      </c>
+      <c r="E142" s="3">
+        <v>73</v>
+      </c>
+      <c r="F142" s="4">
+        <v>1.1643835616438356</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C143" s="2">
+        <v>8</v>
+      </c>
+      <c r="D143" s="3">
+        <v>81</v>
+      </c>
+      <c r="E143" s="3">
+        <v>71</v>
+      </c>
+      <c r="F143" s="4">
+        <v>1.1408450704225352</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C144" s="2">
+        <v>9</v>
+      </c>
+      <c r="D144" s="3">
+        <v>86</v>
+      </c>
+      <c r="E144" s="3">
+        <v>74</v>
+      </c>
+      <c r="F144" s="4">
+        <v>1.1621621621621621</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C145" s="2">
+        <v>10</v>
+      </c>
+      <c r="D145" s="3">
+        <v>107</v>
+      </c>
+      <c r="E145" s="3">
+        <v>95</v>
+      </c>
+      <c r="F145" s="4">
+        <v>1.1263157894736842</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C146" s="2">
+        <v>11</v>
+      </c>
+      <c r="D146" s="3">
+        <v>79</v>
+      </c>
+      <c r="E146" s="3">
+        <v>65</v>
+      </c>
+      <c r="F146" s="4">
+        <v>1.2153846153846153</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C147" s="2">
+        <v>12</v>
+      </c>
+      <c r="D147" s="3">
+        <v>81</v>
+      </c>
+      <c r="E147" s="3">
+        <v>68</v>
+      </c>
+      <c r="F147" s="4">
+        <v>1.1911764705882353</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="3">
+        <v>75</v>
+      </c>
+      <c r="E148" s="3">
+        <v>70</v>
+      </c>
+      <c r="F148" s="4">
+        <v>1.0714285714285714</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C149" s="2">
+        <v>2</v>
+      </c>
+      <c r="D149" s="3">
+        <v>77</v>
+      </c>
+      <c r="E149" s="3">
+        <v>71</v>
+      </c>
+      <c r="F149" s="4">
+        <v>1.0845070422535212</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C150" s="2">
+        <v>3</v>
+      </c>
+      <c r="D150" s="3">
+        <v>91</v>
+      </c>
+      <c r="E150" s="3">
+        <v>86</v>
+      </c>
+      <c r="F150" s="4">
+        <v>1.058139534883721</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C151" s="2">
+        <v>4</v>
+      </c>
+      <c r="D151" s="3">
+        <v>88</v>
+      </c>
+      <c r="E151" s="3">
+        <v>76</v>
+      </c>
+      <c r="F151" s="4">
+        <v>1.1578947368421053</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
         <v>16</v>
       </c>
-      <c r="B132" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C132" s="2">
+      <c r="B152" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C152" s="2">
+        <v>4</v>
+      </c>
+      <c r="D152" s="3">
+        <v>1</v>
+      </c>
+      <c r="E152" s="3">
+        <v>43</v>
+      </c>
+      <c r="F152" s="4">
+        <v>2.3255813953488372E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>16</v>
+      </c>
+      <c r="B153" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C153" s="2">
+        <v>11</v>
+      </c>
+      <c r="D153" s="3">
+        <v>1</v>
+      </c>
+      <c r="E153" s="3">
+        <v>557</v>
+      </c>
+      <c r="F153" s="4">
+        <v>1.7953321364452424E-3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>16</v>
+      </c>
+      <c r="B154" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C154" s="2">
         <v>12</v>
       </c>
-      <c r="D132" s="3">
-        <v>1</v>
-      </c>
-      <c r="E132" s="3">
+      <c r="D154" s="3">
+        <v>1</v>
+      </c>
+      <c r="E154" s="3">
         <v>567</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F154" s="4">
         <v>1.7636684303350969E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>16</v>
+      </c>
+      <c r="B155" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C155" s="2">
+        <v>4</v>
+      </c>
+      <c r="D155" s="3">
+        <v>61</v>
+      </c>
+      <c r="E155" s="3">
+        <v>593</v>
+      </c>
+      <c r="F155" s="4">
+        <v>0.10286677908937605</v>
       </c>
     </row>
   </sheetData>

--- a/upload/plano-cuidado-multi.xlsx
+++ b/upload/plano-cuidado-multi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="17">
   <si>
     <t>unidade</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1125,22 +1125,22 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" s="2">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C37" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D37" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E37" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F37" s="4">
-        <v>3.0303030303030304E-2</v>
+        <v>0.4838709677419355</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1148,19 +1148,19 @@
         <v>7</v>
       </c>
       <c r="B38" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
       </c>
       <c r="E38" s="3">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F38" s="4">
-        <v>2.2222222222222223E-2</v>
+        <v>3.0303030303030304E-2</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1171,16 +1171,16 @@
         <v>2023</v>
       </c>
       <c r="C39" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
       </c>
       <c r="E39" s="3">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F39" s="4">
-        <v>3.4482758620689655E-2</v>
+        <v>2.2222222222222223E-2</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1191,16 +1191,16 @@
         <v>2023</v>
       </c>
       <c r="C40" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="3">
         <v>29</v>
       </c>
       <c r="F40" s="4">
-        <v>6.8965517241379309E-2</v>
+        <v>3.4482758620689655E-2</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1211,16 +1211,16 @@
         <v>2023</v>
       </c>
       <c r="C41" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41" s="3">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F41" s="4">
-        <v>8.8888888888888892E-2</v>
+        <v>6.8965517241379309E-2</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1228,19 +1228,19 @@
         <v>7</v>
       </c>
       <c r="B42" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D42" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F42" s="4">
-        <v>4.3478260869565216E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1251,16 +1251,16 @@
         <v>2024</v>
       </c>
       <c r="C43" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F43" s="4">
-        <v>0.02</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1271,16 +1271,16 @@
         <v>2024</v>
       </c>
       <c r="C44" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E44" s="3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F44" s="4">
-        <v>0.13461538461538461</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1291,16 +1291,16 @@
         <v>2024</v>
       </c>
       <c r="C45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E45" s="3">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F45" s="4">
-        <v>0.28947368421052633</v>
+        <v>0.13461538461538461</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1311,16 +1311,16 @@
         <v>2024</v>
       </c>
       <c r="C46" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" s="3">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F46" s="4">
-        <v>0.30303030303030304</v>
+        <v>0.28947368421052633</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1331,36 +1331,36 @@
         <v>2024</v>
       </c>
       <c r="C47" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E47" s="3">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F47" s="4">
-        <v>0.47499999999999998</v>
+        <v>0.30303030303030304</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C48" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E48" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F48" s="4">
-        <v>1</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1368,39 +1368,39 @@
         <v>8</v>
       </c>
       <c r="B49" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C49" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
       <c r="E49" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4">
-        <v>5.2631578947368418E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="2">
         <v>2024</v>
       </c>
       <c r="C50" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
       </c>
       <c r="E50" s="3">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F50" s="4">
-        <v>1.4705882352941176E-2</v>
+        <v>5.2631578947368418E-2</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1411,16 +1411,16 @@
         <v>2024</v>
       </c>
       <c r="C51" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
       </c>
       <c r="E51" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F51" s="4">
-        <v>1.3157894736842105E-2</v>
+        <v>1.4705882352941176E-2</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1431,16 +1431,16 @@
         <v>2024</v>
       </c>
       <c r="C52" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
       </c>
       <c r="E52" s="3">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F52" s="4">
-        <v>1.2345679012345678E-2</v>
+        <v>1.3157894736842105E-2</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1451,16 +1451,16 @@
         <v>2024</v>
       </c>
       <c r="C53" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
       </c>
       <c r="E53" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F53" s="4">
-        <v>1.1627906976744186E-2</v>
+        <v>1.2345679012345678E-2</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1468,19 +1468,19 @@
         <v>9</v>
       </c>
       <c r="B54" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C54" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D54" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E54" s="3">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F54" s="4">
-        <v>5.7142857142857141E-2</v>
+        <v>1.1627906976744186E-2</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1491,16 +1491,16 @@
         <v>2025</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E55" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F55" s="4">
-        <v>1.4705882352941176E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1511,16 +1511,16 @@
         <v>2025</v>
       </c>
       <c r="C56" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E56" s="3">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F56" s="4">
-        <v>0.12820512820512819</v>
+        <v>1.4705882352941176E-2</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1531,16 +1531,16 @@
         <v>2025</v>
       </c>
       <c r="C57" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E57" s="3">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F57" s="4">
-        <v>0.2</v>
+        <v>0.12820512820512819</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1551,16 +1551,16 @@
         <v>2025</v>
       </c>
       <c r="C58" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" s="3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E58" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F58" s="4">
-        <v>0.35294117647058826</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1571,16 +1571,16 @@
         <v>2025</v>
       </c>
       <c r="C59" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E59" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F59" s="4">
-        <v>0.42424242424242425</v>
+        <v>0.35294117647058826</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1591,16 +1591,16 @@
         <v>2025</v>
       </c>
       <c r="C60" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D60" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E60" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F60" s="4">
-        <v>0.26153846153846155</v>
+        <v>0.42424242424242425</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1611,16 +1611,16 @@
         <v>2025</v>
       </c>
       <c r="C61" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E61" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F61" s="4">
-        <v>0.29850746268656714</v>
+        <v>0.26153846153846155</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1631,16 +1631,16 @@
         <v>2025</v>
       </c>
       <c r="C62" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" s="3">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E62" s="3">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F62" s="4">
-        <v>0.39189189189189189</v>
+        <v>0.29850746268656714</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -1651,16 +1651,16 @@
         <v>2025</v>
       </c>
       <c r="C63" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D63" s="3">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E63" s="3">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F63" s="4">
-        <v>0.28358208955223879</v>
+        <v>0.39189189189189189</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -1671,16 +1671,16 @@
         <v>2025</v>
       </c>
       <c r="C64" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D64" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E64" s="3">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F64" s="4">
-        <v>0.34920634920634919</v>
+        <v>0.28358208955223879</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -1691,16 +1691,16 @@
         <v>2025</v>
       </c>
       <c r="C65" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" s="3">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E65" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F65" s="4">
-        <v>0.22580645161290322</v>
+        <v>0.34920634920634919</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -1708,19 +1708,19 @@
         <v>9</v>
       </c>
       <c r="B66" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D66" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F66" s="4">
-        <v>0.23809523809523808</v>
+        <v>0.22580645161290322</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -1731,16 +1731,16 @@
         <v>2026</v>
       </c>
       <c r="C67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E67" s="3">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F67" s="4">
-        <v>0.23684210526315788</v>
+        <v>0.23809523809523808</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -1751,16 +1751,16 @@
         <v>2026</v>
       </c>
       <c r="C68" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E68" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F68" s="4">
-        <v>0.21333333333333335</v>
+        <v>0.23684210526315788</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -1771,56 +1771,56 @@
         <v>2026</v>
       </c>
       <c r="C69" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D69" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E69" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F69" s="4">
-        <v>0.35135135135135137</v>
+        <v>0.21333333333333335</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B70" s="2">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C70" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D70" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E70" s="3">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F70" s="4">
-        <v>9.0909090909090912E-2</v>
+        <v>0.36486486486486486</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B71" s="2">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C71" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D71" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E71" s="3">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="F71" s="4">
-        <v>0.33333333333333331</v>
+        <v>0.28125</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -1828,19 +1828,19 @@
         <v>10</v>
       </c>
       <c r="B72" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C72" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
       </c>
       <c r="E72" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F72" s="4">
-        <v>0.33333333333333331</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -1848,19 +1848,19 @@
         <v>10</v>
       </c>
       <c r="B73" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C73" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
       </c>
       <c r="E73" s="3">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F73" s="4">
-        <v>1.7543859649122806E-2</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -1868,19 +1868,19 @@
         <v>10</v>
       </c>
       <c r="B74" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C74" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
       </c>
       <c r="E74" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F74" s="4">
-        <v>0.5</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -1891,16 +1891,16 @@
         <v>2024</v>
       </c>
       <c r="C75" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
       </c>
       <c r="E75" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F75" s="4">
-        <v>0.1111111111111111</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -1908,19 +1908,19 @@
         <v>10</v>
       </c>
       <c r="B76" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C76" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D76" s="3">
         <v>1</v>
       </c>
       <c r="E76" s="3">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F76" s="4">
-        <v>9.0909090909090912E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -1928,19 +1928,19 @@
         <v>10</v>
       </c>
       <c r="B77" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C77" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D77" s="3">
         <v>1</v>
       </c>
       <c r="E77" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F77" s="4">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -1948,19 +1948,19 @@
         <v>10</v>
       </c>
       <c r="B78" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C78" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D78" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F78" s="4">
-        <v>0.2857142857142857</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -1971,16 +1971,16 @@
         <v>2025</v>
       </c>
       <c r="C79" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79" s="3">
         <v>1</v>
       </c>
       <c r="E79" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F79" s="4">
-        <v>0.2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -1991,16 +1991,16 @@
         <v>2025</v>
       </c>
       <c r="C80" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3">
         <v>1</v>
       </c>
       <c r="E80" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" s="4">
-        <v>0.14285714285714285</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2011,16 +2011,16 @@
         <v>2025</v>
       </c>
       <c r="C81" s="2">
+        <v>4</v>
+      </c>
+      <c r="D81" s="3">
+        <v>2</v>
+      </c>
+      <c r="E81" s="3">
         <v>7</v>
       </c>
-      <c r="D81" s="3">
-        <v>1</v>
-      </c>
-      <c r="E81" s="3">
-        <v>8</v>
-      </c>
       <c r="F81" s="4">
-        <v>0.125</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2031,16 +2031,16 @@
         <v>2025</v>
       </c>
       <c r="C82" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D82" s="3">
         <v>1</v>
       </c>
       <c r="E82" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F82" s="4">
-        <v>7.6923076923076927E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2051,16 +2051,16 @@
         <v>2025</v>
       </c>
       <c r="C83" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D83" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F83" s="4">
-        <v>0.1</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2071,16 +2071,16 @@
         <v>2025</v>
       </c>
       <c r="C84" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D84" s="3">
         <v>1</v>
       </c>
       <c r="E84" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F84" s="4">
-        <v>7.1428571428571425E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2091,16 +2091,16 @@
         <v>2025</v>
       </c>
       <c r="C85" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D85" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E85" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F85" s="4">
-        <v>0.1875</v>
+        <v>7.6923076923076927E-2</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2108,19 +2108,19 @@
         <v>10</v>
       </c>
       <c r="B86" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D86" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F86" s="4">
-        <v>0.15789473684210525</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2128,19 +2128,19 @@
         <v>10</v>
       </c>
       <c r="B87" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C87" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D87" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" s="3">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F87" s="4">
-        <v>6.9767441860465115E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2148,44 +2148,44 @@
         <v>10</v>
       </c>
       <c r="B88" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C88" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D88" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E88" s="3">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="F88" s="4">
-        <v>0.10344827586206896</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B89" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C89" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D89" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E89" s="3">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="F89" s="4">
-        <v>1.5544041450777202E-2</v>
+        <v>0.21052631578947367</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B90" s="2">
         <v>2026</v>
@@ -2194,133 +2194,133 @@
         <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" s="3">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="F90" s="4">
-        <v>6.5789473684210523E-3</v>
+        <v>8.8235294117647065E-2</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B91" s="2">
         <v>2026</v>
       </c>
       <c r="C91" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D91" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E91" s="3">
-        <v>788</v>
+        <v>58</v>
       </c>
       <c r="F91" s="4">
-        <v>1.2690355329949238E-3</v>
+        <v>0.1206896551724138</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B92" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C92" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D92" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E92" s="3">
-        <v>328</v>
+        <v>51</v>
       </c>
       <c r="F92" s="4">
-        <v>3.0487804878048782E-3</v>
+        <v>0.11764705882352941</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B93" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C93" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D93" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E93" s="3">
-        <v>375</v>
+        <v>193</v>
       </c>
       <c r="F93" s="4">
-        <v>3.2000000000000001E-2</v>
+        <v>1.5544041450777202E-2</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B94" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C94" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D94" s="3">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="E94" s="3">
-        <v>352</v>
+        <v>152</v>
       </c>
       <c r="F94" s="4">
-        <v>0.21022727272727273</v>
+        <v>6.5789473684210523E-3</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B95" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C95" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D95" s="3">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="E95" s="3">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F95" s="4">
-        <v>0.5</v>
+        <v>6.0975609756097563E-3</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B96" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C96" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D96" s="3">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="E96" s="3">
-        <v>230</v>
+        <v>788</v>
       </c>
       <c r="F96" s="4">
-        <v>0.39565217391304347</v>
+        <v>1.2690355329949238E-3</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2331,16 +2331,16 @@
         <v>2024</v>
       </c>
       <c r="C97" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D97" s="3">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="E97" s="3">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="F97" s="4">
-        <v>0.37956204379562042</v>
+        <v>3.0487804878048782E-3</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2348,19 +2348,19 @@
         <v>13</v>
       </c>
       <c r="B98" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C98" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D98" s="3">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="E98" s="3">
-        <v>285</v>
+        <v>375</v>
       </c>
       <c r="F98" s="4">
-        <v>0.57894736842105265</v>
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2368,19 +2368,19 @@
         <v>13</v>
       </c>
       <c r="B99" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C99" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D99" s="3">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="E99" s="3">
-        <v>243</v>
+        <v>352</v>
       </c>
       <c r="F99" s="4">
-        <v>0.85185185185185186</v>
+        <v>0.21022727272727273</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2388,19 +2388,19 @@
         <v>13</v>
       </c>
       <c r="B100" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C100" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D100" s="3">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="E100" s="3">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="F100" s="4">
-        <v>0.84642857142857142</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -2408,19 +2408,19 @@
         <v>13</v>
       </c>
       <c r="B101" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C101" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D101" s="3">
-        <v>221</v>
+        <v>91</v>
       </c>
       <c r="E101" s="3">
-        <v>272</v>
+        <v>230</v>
       </c>
       <c r="F101" s="4">
-        <v>0.8125</v>
+        <v>0.39565217391304347</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2428,19 +2428,19 @@
         <v>13</v>
       </c>
       <c r="B102" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C102" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D102" s="3">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="E102" s="3">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="F102" s="4">
-        <v>0.73519163763066198</v>
+        <v>0.37956204379562042</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2451,16 +2451,16 @@
         <v>2025</v>
       </c>
       <c r="C103" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D103" s="3">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="E103" s="3">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F103" s="4">
-        <v>0.79120879120879117</v>
+        <v>0.57894736842105265</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -2471,16 +2471,16 @@
         <v>2025</v>
       </c>
       <c r="C104" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D104" s="3">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E104" s="3">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="F104" s="4">
-        <v>0.73630136986301364</v>
+        <v>0.85185185185185186</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2491,16 +2491,16 @@
         <v>2025</v>
       </c>
       <c r="C105" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D105" s="3">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="E105" s="3">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="F105" s="4">
-        <v>0.79104477611940294</v>
+        <v>0.84642857142857142</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -2511,16 +2511,16 @@
         <v>2025</v>
       </c>
       <c r="C106" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D106" s="3">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="E106" s="3">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="F106" s="4">
-        <v>0.76569037656903771</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -2531,16 +2531,16 @@
         <v>2025</v>
       </c>
       <c r="C107" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D107" s="3">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="E107" s="3">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="F107" s="4">
-        <v>0.66938775510204085</v>
+        <v>0.73519163763066198</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -2551,16 +2551,16 @@
         <v>2025</v>
       </c>
       <c r="C108" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D108" s="3">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="E108" s="3">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="F108" s="4">
-        <v>0.60629921259842523</v>
+        <v>0.79120879120879117</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -2571,16 +2571,16 @@
         <v>2025</v>
       </c>
       <c r="C109" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D109" s="3">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="E109" s="3">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="F109" s="4">
-        <v>0.56106870229007633</v>
+        <v>0.73630136986301364</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -2588,19 +2588,19 @@
         <v>13</v>
       </c>
       <c r="B110" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C110" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D110" s="3">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="E110" s="3">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F110" s="4">
-        <v>0.46886446886446886</v>
+        <v>0.79104477611940294</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -2608,19 +2608,19 @@
         <v>13</v>
       </c>
       <c r="B111" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C111" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D111" s="3">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="E111" s="3">
-        <v>322</v>
+        <v>239</v>
       </c>
       <c r="F111" s="4">
-        <v>0.37267080745341613</v>
+        <v>0.76569037656903771</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2628,19 +2628,19 @@
         <v>13</v>
       </c>
       <c r="B112" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C112" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D112" s="3">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="E112" s="3">
-        <v>325</v>
+        <v>245</v>
       </c>
       <c r="F112" s="4">
-        <v>0.58769230769230774</v>
+        <v>0.66938775510204085</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -2648,159 +2648,159 @@
         <v>13</v>
       </c>
       <c r="B113" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C113" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D113" s="3">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E113" s="3">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="F113" s="4">
-        <v>0.56655290102389078</v>
+        <v>0.60629921259842523</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B114" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C114" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D114" s="3">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="E114" s="3">
-        <v>403</v>
+        <v>262</v>
       </c>
       <c r="F114" s="4">
-        <v>2.4813895781637717E-3</v>
+        <v>0.56106870229007633</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B115" s="2">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C115" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D115" s="3">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="E115" s="3">
-        <v>87</v>
+        <v>273</v>
       </c>
       <c r="F115" s="4">
-        <v>1.1494252873563218E-2</v>
+        <v>0.46886446886446886</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B116" s="2">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C116" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D116" s="3">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="E116" s="3">
-        <v>96</v>
+        <v>322</v>
       </c>
       <c r="F116" s="4">
-        <v>4.1666666666666664E-2</v>
+        <v>0.37267080745341613</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B117" s="2">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C117" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D117" s="3">
-        <v>4</v>
+        <v>192</v>
       </c>
       <c r="E117" s="3">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="F117" s="4">
-        <v>0.05</v>
+        <v>0.59076923076923082</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B118" s="2">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C118" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D118" s="3">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="E118" s="3">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="F118" s="4">
-        <v>0.25</v>
+        <v>0.57337883959044367</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B119" s="2">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C119" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D119" s="3">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="E119" s="3">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="F119" s="4">
-        <v>0.87777777777777777</v>
+        <v>0.47931034482758622</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B120" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C120" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D120" s="3">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E120" s="3">
-        <v>76</v>
+        <v>403</v>
       </c>
       <c r="F120" s="4">
-        <v>0.88157894736842102</v>
+        <v>2.4813895781637717E-3</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -2808,19 +2808,19 @@
         <v>15</v>
       </c>
       <c r="B121" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C121" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D121" s="3">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="E121" s="3">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="F121" s="4">
-        <v>0.92035398230088494</v>
+        <v>1.1494252873563218E-2</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -2831,16 +2831,16 @@
         <v>2023</v>
       </c>
       <c r="C122" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D122" s="3">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="E122" s="3">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F122" s="4">
-        <v>0.84090909090909094</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -2851,16 +2851,16 @@
         <v>2023</v>
       </c>
       <c r="C123" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D123" s="3">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="E123" s="3">
         <v>80</v>
       </c>
       <c r="F123" s="4">
-        <v>1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -2868,19 +2868,19 @@
         <v>15</v>
       </c>
       <c r="B124" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C124" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D124" s="3">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="E124" s="3">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F124" s="4">
-        <v>0.9375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -2888,19 +2888,19 @@
         <v>15</v>
       </c>
       <c r="B125" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C125" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D125" s="3">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E125" s="3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F125" s="4">
-        <v>0.96</v>
+        <v>0.87777777777777777</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -2908,19 +2908,19 @@
         <v>15</v>
       </c>
       <c r="B126" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C126" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D126" s="3">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E126" s="3">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F126" s="4">
-        <v>1.1025641025641026</v>
+        <v>0.88157894736842102</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -2928,19 +2928,19 @@
         <v>15</v>
       </c>
       <c r="B127" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C127" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D127" s="3">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E127" s="3">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F127" s="4">
-        <v>0.92682926829268297</v>
+        <v>0.92035398230088494</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -2948,19 +2948,19 @@
         <v>15</v>
       </c>
       <c r="B128" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C128" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D128" s="3">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E128" s="3">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F128" s="4">
-        <v>1.1884057971014492</v>
+        <v>0.84090909090909094</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -2968,19 +2968,19 @@
         <v>15</v>
       </c>
       <c r="B129" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C129" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D129" s="3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E129" s="3">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F129" s="4">
-        <v>1.0975609756097562</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -2991,16 +2991,16 @@
         <v>2024</v>
       </c>
       <c r="C130" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D130" s="3">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E130" s="3">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F130" s="4">
-        <v>1.0506329113924051</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3011,16 +3011,16 @@
         <v>2024</v>
       </c>
       <c r="C131" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D131" s="3">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E131" s="3">
         <v>75</v>
       </c>
       <c r="F131" s="4">
-        <v>1.1466666666666667</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3031,16 +3031,16 @@
         <v>2024</v>
       </c>
       <c r="C132" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D132" s="3">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E132" s="3">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="F132" s="4">
-        <v>1.0526315789473684</v>
+        <v>1.1025641025641026</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3051,16 +3051,16 @@
         <v>2024</v>
       </c>
       <c r="C133" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D133" s="3">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E133" s="3">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F133" s="4">
-        <v>1.1176470588235294</v>
+        <v>0.92682926829268297</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3071,16 +3071,16 @@
         <v>2024</v>
       </c>
       <c r="C134" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D134" s="3">
         <v>82</v>
       </c>
       <c r="E134" s="3">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F134" s="4">
-        <v>1.3225806451612903</v>
+        <v>1.1884057971014492</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3091,16 +3091,16 @@
         <v>2024</v>
       </c>
       <c r="C135" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D135" s="3">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E135" s="3">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F135" s="4">
-        <v>1.4727272727272727</v>
+        <v>1.0975609756097562</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3108,19 +3108,19 @@
         <v>15</v>
       </c>
       <c r="B136" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D136" s="3">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E136" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F136" s="4">
-        <v>1.2948717948717949</v>
+        <v>1.0506329113924051</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3128,19 +3128,19 @@
         <v>15</v>
       </c>
       <c r="B137" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C137" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D137" s="3">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="E137" s="3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F137" s="4">
-        <v>1.2181818181818183</v>
+        <v>1.1466666666666667</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3148,19 +3148,19 @@
         <v>15</v>
       </c>
       <c r="B138" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C138" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D138" s="3">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="E138" s="3">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F138" s="4">
-        <v>1.2051282051282051</v>
+        <v>1.0526315789473684</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3168,19 +3168,19 @@
         <v>15</v>
       </c>
       <c r="B139" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C139" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D139" s="3">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E139" s="3">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F139" s="4">
-        <v>1.1481481481481481</v>
+        <v>1.1176470588235294</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3188,19 +3188,19 @@
         <v>15</v>
       </c>
       <c r="B140" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C140" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D140" s="3">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E140" s="3">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F140" s="4">
-        <v>1.0547945205479452</v>
+        <v>1.3225806451612903</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3208,19 +3208,19 @@
         <v>15</v>
       </c>
       <c r="B141" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C141" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D141" s="3">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E141" s="3">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F141" s="4">
-        <v>1.1097560975609757</v>
+        <v>1.4727272727272727</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3231,16 +3231,16 @@
         <v>2025</v>
       </c>
       <c r="C142" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D142" s="3">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E142" s="3">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F142" s="4">
-        <v>1.1643835616438356</v>
+        <v>1.2948717948717949</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3251,16 +3251,16 @@
         <v>2025</v>
       </c>
       <c r="C143" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D143" s="3">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E143" s="3">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="F143" s="4">
-        <v>1.1408450704225352</v>
+        <v>1.2181818181818183</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3271,16 +3271,16 @@
         <v>2025</v>
       </c>
       <c r="C144" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D144" s="3">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E144" s="3">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F144" s="4">
-        <v>1.1621621621621621</v>
+        <v>1.2051282051282051</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3291,16 +3291,16 @@
         <v>2025</v>
       </c>
       <c r="C145" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D145" s="3">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E145" s="3">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F145" s="4">
-        <v>1.1263157894736842</v>
+        <v>1.1481481481481481</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3311,16 +3311,16 @@
         <v>2025</v>
       </c>
       <c r="C146" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D146" s="3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E146" s="3">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F146" s="4">
-        <v>1.2153846153846153</v>
+        <v>1.0547945205479452</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -3331,16 +3331,16 @@
         <v>2025</v>
       </c>
       <c r="C147" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D147" s="3">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E147" s="3">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="F147" s="4">
-        <v>1.1911764705882353</v>
+        <v>1.1097560975609757</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3348,19 +3348,19 @@
         <v>15</v>
       </c>
       <c r="B148" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C148" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D148" s="3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E148" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F148" s="4">
-        <v>1.0714285714285714</v>
+        <v>1.1643835616438356</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3368,19 +3368,19 @@
         <v>15</v>
       </c>
       <c r="B149" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C149" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D149" s="3">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E149" s="3">
         <v>71</v>
       </c>
       <c r="F149" s="4">
-        <v>1.0845070422535212</v>
+        <v>1.1408450704225352</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3388,19 +3388,19 @@
         <v>15</v>
       </c>
       <c r="B150" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C150" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D150" s="3">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E150" s="3">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F150" s="4">
-        <v>1.058139534883721</v>
+        <v>1.1621621621621621</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -3408,99 +3408,259 @@
         <v>15</v>
       </c>
       <c r="B151" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C151" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D151" s="3">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="E151" s="3">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F151" s="4">
-        <v>1.1578947368421053</v>
+        <v>1.1263157894736842</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B152" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C152" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D152" s="3">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="E152" s="3">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F152" s="4">
-        <v>2.3255813953488372E-2</v>
+        <v>1.2153846153846153</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B153" s="2">
         <v>2025</v>
       </c>
       <c r="C153" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D153" s="3">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="E153" s="3">
-        <v>557</v>
+        <v>68</v>
       </c>
       <c r="F153" s="4">
-        <v>1.7953321364452424E-3</v>
+        <v>1.1911764705882353</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B154" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C154" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D154" s="3">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E154" s="3">
-        <v>567</v>
+        <v>70</v>
       </c>
       <c r="F154" s="4">
-        <v>1.7636684303350969E-3</v>
+        <v>1.0714285714285714</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
       </c>
       <c r="C155" s="2">
+        <v>2</v>
+      </c>
+      <c r="D155" s="3">
+        <v>77</v>
+      </c>
+      <c r="E155" s="3">
+        <v>71</v>
+      </c>
+      <c r="F155" s="4">
+        <v>1.0845070422535212</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C156" s="2">
+        <v>3</v>
+      </c>
+      <c r="D156" s="3">
+        <v>91</v>
+      </c>
+      <c r="E156" s="3">
+        <v>86</v>
+      </c>
+      <c r="F156" s="4">
+        <v>1.058139534883721</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C157" s="2">
         <v>4</v>
       </c>
-      <c r="D155" s="3">
+      <c r="D157" s="3">
+        <v>88</v>
+      </c>
+      <c r="E157" s="3">
+        <v>73</v>
+      </c>
+      <c r="F157" s="4">
+        <v>1.2054794520547945</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C158" s="2">
+        <v>5</v>
+      </c>
+      <c r="D158" s="3">
+        <v>94</v>
+      </c>
+      <c r="E158" s="3">
+        <v>89</v>
+      </c>
+      <c r="F158" s="4">
+        <v>1.0561797752808988</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>16</v>
+      </c>
+      <c r="B159" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C159" s="2">
+        <v>4</v>
+      </c>
+      <c r="D159" s="3">
+        <v>1</v>
+      </c>
+      <c r="E159" s="3">
+        <v>43</v>
+      </c>
+      <c r="F159" s="4">
+        <v>2.3255813953488372E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>16</v>
+      </c>
+      <c r="B160" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C160" s="2">
+        <v>11</v>
+      </c>
+      <c r="D160" s="3">
+        <v>1</v>
+      </c>
+      <c r="E160" s="3">
+        <v>557</v>
+      </c>
+      <c r="F160" s="4">
+        <v>1.7953321364452424E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>16</v>
+      </c>
+      <c r="B161" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C161" s="2">
+        <v>12</v>
+      </c>
+      <c r="D161" s="3">
+        <v>1</v>
+      </c>
+      <c r="E161" s="3">
+        <v>567</v>
+      </c>
+      <c r="F161" s="4">
+        <v>1.7636684303350969E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>16</v>
+      </c>
+      <c r="B162" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C162" s="2">
+        <v>4</v>
+      </c>
+      <c r="D162" s="3">
         <v>61</v>
       </c>
-      <c r="E155" s="3">
+      <c r="E162" s="3">
         <v>593</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F162" s="4">
         <v>0.10286677908937605</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>16</v>
+      </c>
+      <c r="B163" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C163" s="2">
+        <v>5</v>
+      </c>
+      <c r="D163" s="3">
+        <v>92</v>
+      </c>
+      <c r="E163" s="3">
+        <v>616</v>
+      </c>
+      <c r="F163" s="4">
+        <v>0.14935064935064934</v>
       </c>
     </row>
   </sheetData>
